--- a/sheets/조재수대금교본/검수/산골 소년의 사랑 이야기.xlsx
+++ b/sheets/조재수대금교본/검수/산골 소년의 사랑 이야기.xlsx
@@ -3363,19 +3363,11 @@
     </row>
     <row r="4" ht="90.2" customHeight="true">
       <c r="A4" s="0"/>
-      <c r="B4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B4" s="21"/>
       <c r="C4" s="23"/>
       <c r="D4" s="21"/>
       <c r="E4" s="23"/>
-      <c r="F4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F4" s="21"/>
       <c r="G4" s="23"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
@@ -3521,51 +3513,26 @@
       <c r="E7" s="23"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-‹</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="G7" s="23"/>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H7" s="21"/>
       <c r="I7" s="23"/>
       <c r="J7" s="21"/>
       <c r="K7" s="23"/>
-      <c r="L7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L7" s="21"/>
       <c r="M7" s="23"/>
-      <c r="N7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N7" s="21"/>
       <c r="O7" s="23"/>
-      <c r="P7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P7" s="21"/>
       <c r="Q7" s="23"/>
     </row>
     <row r="8" ht="90.2" customHeight="true">
       <c r="A8" s="0"/>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B8" s="21"/>
       <c r="C8" s="24"/>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D8" s="21"/>
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
@@ -3584,8 +3551,7 @@
       <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-林
-‹</t>
+林</t>
         </is>
       </c>
       <c r="K8" s="24"/>
@@ -3699,8 +3665,7 @@
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-‹</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="C11" s="24"/>
@@ -3794,23 +3759,11 @@
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D13" s="21"/>
       <c r="E13" s="23"/>
-      <c r="F13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F13" s="21"/>
       <c r="G13" s="23"/>
-      <c r="H13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H13" s="21"/>
       <c r="I13" s="23"/>
       <c r="J13" s="21"/>
       <c r="K13" s="23"/>

--- a/sheets/조재수대금교본/검수/산골 소년의 사랑 이야기.xlsx
+++ b/sheets/조재수대금교본/검수/산골 소년의 사랑 이야기.xlsx
@@ -3265,28 +3265,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60.61" customHeight="true">
+    <row r="2" ht="64.52" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="90.2" customHeight="true">
+    <row r="3" ht="96.05" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="90.2" customHeight="true">
+    <row r="4" ht="96.05" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" ht="90.2" customHeight="true">
+    <row r="5" ht="96.05" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="Q5" s="24"/>
     </row>
-    <row r="6" ht="90.2" customHeight="true">
+    <row r="6" ht="96.05" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="Q6" s="22"/>
     </row>
-    <row r="7" ht="90.2" customHeight="true">
+    <row r="7" ht="96.05" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
       <c r="P7" s="21"/>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" ht="90.2" customHeight="true">
+    <row r="8" ht="96.05" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="24"/>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="Q8" s="24"/>
     </row>
-    <row r="9" ht="90.2" customHeight="true">
+    <row r="9" ht="96.05" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="Q9" s="22"/>
     </row>
-    <row r="10" ht="90.2" customHeight="true">
+    <row r="10" ht="96.05" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
@@ -3661,7 +3661,7 @@
       <c r="P10" s="21"/>
       <c r="Q10" s="23"/>
     </row>
-    <row r="11" ht="90.2" customHeight="true">
+    <row r="11" ht="96.05" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
       <c r="P11" s="21"/>
       <c r="Q11" s="24"/>
     </row>
-    <row r="12" ht="90.2" customHeight="true">
+    <row r="12" ht="96.05" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="Q12" s="22"/>
     </row>
-    <row r="13" ht="90.2" customHeight="true">
+    <row r="13" ht="96.05" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -3774,7 +3774,7 @@
       <c r="P13" s="21"/>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="90.2" customHeight="true">
+    <row r="14" ht="96.05" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3838,6 +3838,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
 </worksheet>
 </file>